--- a/data/学生成绩表.xlsx
+++ b/data/学生成绩表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22860" windowHeight="10800"/>
+    <workbookView windowWidth="22860" windowHeight="11600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1577,7 +1577,7 @@
         <v>87</v>
       </c>
       <c r="F11">
-        <v>84</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1874,7 +1874,7 @@
         <v>95</v>
       </c>
       <c r="E26">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F26">
         <v>87</v>
@@ -2134,7 +2134,7 @@
         <v>49</v>
       </c>
       <c r="E39">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F39">
         <v>49</v>
@@ -2334,7 +2334,7 @@
         <v>77</v>
       </c>
       <c r="E49">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="F49">
         <v>74</v>
@@ -2354,7 +2354,7 @@
         <v>93</v>
       </c>
       <c r="E50">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="F50">
         <v>92</v>
@@ -2374,7 +2374,7 @@
         <v>89</v>
       </c>
       <c r="E51">
-        <v>49</v>
+        <v>-3</v>
       </c>
       <c r="F51">
         <v>89</v>
@@ -2394,7 +2394,7 @@
         <v>75</v>
       </c>
       <c r="E52">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="F52">
         <v>61</v>
@@ -2414,7 +2414,7 @@
         <v>60</v>
       </c>
       <c r="E53">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2434,7 +2434,7 @@
         <v>76</v>
       </c>
       <c r="E54">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="F54">
         <v>67</v>
@@ -2454,7 +2454,7 @@
         <v>81</v>
       </c>
       <c r="E55">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="F55">
         <v>85</v>
@@ -2474,7 +2474,7 @@
         <v>41</v>
       </c>
       <c r="E56">
-        <v>98</v>
+        <v>1000</v>
       </c>
       <c r="F56">
         <v>70</v>

--- a/data/学生成绩表.xlsx
+++ b/data/学生成绩表.xlsx
@@ -2374,7 +2374,7 @@
         <v>89</v>
       </c>
       <c r="E51">
-        <v>-3</v>
+        <v>50</v>
       </c>
       <c r="F51">
         <v>89</v>
@@ -2394,7 +2394,7 @@
         <v>75</v>
       </c>
       <c r="E52">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="F52">
         <v>61</v>
@@ -2414,7 +2414,7 @@
         <v>60</v>
       </c>
       <c r="E53">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2454,7 +2454,7 @@
         <v>81</v>
       </c>
       <c r="E55">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="F55">
         <v>85</v>
@@ -2474,7 +2474,7 @@
         <v>41</v>
       </c>
       <c r="E56">
-        <v>1000</v>
+        <v>98</v>
       </c>
       <c r="F56">
         <v>70</v>

--- a/data/学生成绩表.xlsx
+++ b/data/学生成绩表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="64">
   <si>
     <t>学号</t>
   </si>
@@ -35,6 +35,9 @@
     <t>姓名</t>
   </si>
   <si>
+    <t>性别</t>
+  </si>
+  <si>
     <t>班级</t>
   </si>
   <si>
@@ -50,7 +53,13 @@
     <t>张三</t>
   </si>
   <si>
+    <t>男</t>
+  </si>
+  <si>
     <t>李四</t>
+  </si>
+  <si>
+    <t>女</t>
   </si>
   <si>
     <t>王五</t>
@@ -1357,10 +1366,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F56"/>
-  <sheetFormatPr defaultColWidth="8.609375" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <dimension ref="A1:G56"/>
+  <sheetFormatPr defaultColWidth="8.609375" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1379,1104 +1388,1272 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>202601</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>85</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>92</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>202602</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>76</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>68</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>202603</v>
       </c>
       <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>1</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>90</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>88</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>202604</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5">
         <v>3</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>59</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>62</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>202605</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6">
         <v>4</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>88</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>95</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>202606</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7">
         <v>2</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>72</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>85</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>202607</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8">
         <v>4</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>96</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>80</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>202608</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9">
         <v>3</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>59</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>79</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>202609</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10">
         <v>3</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>55</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>94</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>202610</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11">
         <v>5</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>51</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>87</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>202611</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12">
         <v>3</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>96</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>94</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>202612</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13">
         <v>4</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>61</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>64</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>202613</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14">
         <v>2</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>63</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>82</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>202614</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15">
         <v>3</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>61</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>51</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>202615</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16">
         <v>1</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>58</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>79</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>202616</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17">
         <v>2</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>56</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>45</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>202617</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18">
         <v>1</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>80</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>93</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>202618</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19">
         <v>5</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>56</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>91</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>96</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>202619</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20">
         <v>3</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>42</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>65</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>202620</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21">
+        <v>28</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21">
         <v>2</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>83</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>99</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>202621</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22">
         <v>4</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>72</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>81</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>202622</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23">
         <v>4</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>89</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>93</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>202623</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24">
+        <v>31</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24">
         <v>5</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>73</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>65</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>202624</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25">
         <v>4</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>53</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>72</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>202625</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26">
+        <v>33</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26">
         <v>4</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>95</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>25</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>202626</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27">
+        <v>34</v>
+      </c>
+      <c r="C27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27">
         <v>2</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>62</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>82</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>202627</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28">
+        <v>35</v>
+      </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28">
         <v>3</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>70</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>63</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>202628</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29">
+        <v>36</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29">
         <v>3</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>77</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>49</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>202629</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30">
+        <v>37</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30">
         <v>3</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>52</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>70</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>202630</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31">
+        <v>38</v>
+      </c>
+      <c r="C31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31">
         <v>3</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>52</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>61</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>202631</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32">
+        <v>39</v>
+      </c>
+      <c r="C32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32">
         <v>2</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>93</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>51</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>202632</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33">
+        <v>40</v>
+      </c>
+      <c r="C33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33">
         <v>5</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>70</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>74</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>202633</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34">
+        <v>41</v>
+      </c>
+      <c r="C34" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34">
         <v>2</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>57</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>97</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>202634</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35">
+        <v>42</v>
+      </c>
+      <c r="C35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35">
         <v>2</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>50</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>52</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>202635</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36">
+        <v>43</v>
+      </c>
+      <c r="C36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36">
         <v>3</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>60</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>94</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>87</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>202636</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37">
+        <v>44</v>
+      </c>
+      <c r="C37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37">
         <v>4</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>89</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>59</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>202637</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38">
+        <v>45</v>
+      </c>
+      <c r="C38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38">
         <v>1</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>96</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>53</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>202638</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39">
+        <v>46</v>
+      </c>
+      <c r="C39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39">
         <v>2</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>49</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>20</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>202639</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40">
+        <v>47</v>
+      </c>
+      <c r="C40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40">
         <v>2</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>73</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>93</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>202640</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41">
+        <v>48</v>
+      </c>
+      <c r="C41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41">
         <v>2</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>56</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>95</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>202641</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42">
+        <v>49</v>
+      </c>
+      <c r="C42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42">
         <v>1</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>92</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>95</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>202642</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
-      </c>
-      <c r="C43">
+        <v>50</v>
+      </c>
+      <c r="C43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43">
         <v>1</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>53</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>72</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>71</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>202643</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
-      </c>
-      <c r="C44">
+        <v>51</v>
+      </c>
+      <c r="C44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44">
         <v>1</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>58</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>86</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>69</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>202644</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
-      </c>
-      <c r="C45">
+        <v>52</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45">
         <v>5</v>
       </c>
-      <c r="D45">
+      <c r="E45">
         <v>56</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>70</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <v>81</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>202645</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
-      </c>
-      <c r="C46">
+        <v>53</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46">
         <v>5</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>95</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>78</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>74</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>202646</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
-      </c>
-      <c r="C47">
+        <v>54</v>
+      </c>
+      <c r="C47" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47">
         <v>3</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>94</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>95</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>74</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>202647</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
-      </c>
-      <c r="C48">
+        <v>55</v>
+      </c>
+      <c r="C48" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48">
         <v>3</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>46</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>47</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>93</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>202648</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
-      </c>
-      <c r="C49">
+        <v>56</v>
+      </c>
+      <c r="C49" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49">
         <v>3</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>77</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>56</v>
       </c>
-      <c r="F49">
+      <c r="G49">
         <v>74</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:7">
       <c r="A50">
         <v>202649</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
-      </c>
-      <c r="C50">
+        <v>57</v>
+      </c>
+      <c r="C50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50">
         <v>1</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>93</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>56</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>92</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:7">
       <c r="A51">
         <v>202650</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
-      </c>
-      <c r="C51">
+        <v>58</v>
+      </c>
+      <c r="C51" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51">
         <v>4</v>
       </c>
-      <c r="D51">
+      <c r="E51">
         <v>89</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>50</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>89</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:7">
       <c r="A52">
         <v>202651</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
-      </c>
-      <c r="C52">
+        <v>59</v>
+      </c>
+      <c r="C52" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52">
         <v>2</v>
       </c>
-      <c r="D52">
+      <c r="E52">
         <v>75</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>72</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:7">
       <c r="A53">
         <v>202652</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
-      </c>
-      <c r="C53">
+        <v>60</v>
+      </c>
+      <c r="C53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53">
         <v>3</v>
       </c>
-      <c r="D53">
+      <c r="E53">
         <v>60</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>89</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:7">
       <c r="A54">
         <v>202653</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
-      </c>
-      <c r="C54">
+        <v>61</v>
+      </c>
+      <c r="C54" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54">
         <v>4</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <v>76</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>100</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>67</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:7">
       <c r="A55">
         <v>202654</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
-      </c>
-      <c r="C55">
+        <v>62</v>
+      </c>
+      <c r="C55" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55">
         <v>4</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <v>81</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>53</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>85</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:7">
       <c r="A56">
         <v>202655</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
-      </c>
-      <c r="C56">
+        <v>63</v>
+      </c>
+      <c r="C56" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56">
         <v>1</v>
       </c>
-      <c r="D56">
+      <c r="E56">
         <v>41</v>
       </c>
-      <c r="E56">
+      <c r="F56">
         <v>98</v>
       </c>
-      <c r="F56">
+      <c r="G56">
         <v>70</v>
       </c>
     </row>

--- a/data/学生成绩表.xlsx
+++ b/data/学生成绩表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22860" windowHeight="11600"/>
+    <workbookView windowWidth="17760" windowHeight="11600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="149">
   <si>
     <t>学号</t>
   </si>
@@ -50,6 +50,12 @@
     <t>英语</t>
   </si>
   <si>
+    <t>物理</t>
+  </si>
+  <si>
+    <t>化学</t>
+  </si>
+  <si>
     <t>张三</t>
   </si>
   <si>
@@ -219,6 +225,255 @@
   </si>
   <si>
     <t>吴书瑶</t>
+  </si>
+  <si>
+    <t>陈曦</t>
+  </si>
+  <si>
+    <t>李想</t>
+  </si>
+  <si>
+    <t>王璐瑶</t>
+  </si>
+  <si>
+    <t>赵雪晴</t>
+  </si>
+  <si>
+    <t>孙浩宇</t>
+  </si>
+  <si>
+    <t>周若琳</t>
+  </si>
+  <si>
+    <t>吴子涵</t>
+  </si>
+  <si>
+    <t>郭雅静</t>
+  </si>
+  <si>
+    <t>唐雅茹</t>
+  </si>
+  <si>
+    <t>沈佳宜</t>
+  </si>
+  <si>
+    <t>宋佳音</t>
+  </si>
+  <si>
+    <t>欧阳雪</t>
+  </si>
+  <si>
+    <t>慕容枫</t>
+  </si>
+  <si>
+    <t>令狐冲</t>
+  </si>
+  <si>
+    <t>李慕白</t>
+  </si>
+  <si>
+    <t>王小蒙</t>
+  </si>
+  <si>
+    <t>李娜</t>
+  </si>
+  <si>
+    <t>周涛</t>
+  </si>
+  <si>
+    <t>郑爽</t>
+  </si>
+  <si>
+    <t>郭晨</t>
+  </si>
+  <si>
+    <t>唐欣</t>
+  </si>
+  <si>
+    <t>沈月</t>
+  </si>
+  <si>
+    <t>宋阳</t>
+  </si>
+  <si>
+    <t>欧阳夏</t>
+  </si>
+  <si>
+    <t>慕容晴</t>
+  </si>
+  <si>
+    <t>上官云</t>
+  </si>
+  <si>
+    <t>司马光</t>
+  </si>
+  <si>
+    <t>诸葛明</t>
+  </si>
+  <si>
+    <t>东方白</t>
+  </si>
+  <si>
+    <t>西门吹雪</t>
+  </si>
+  <si>
+    <t>独孤求败</t>
+  </si>
+  <si>
+    <t>李清风</t>
+  </si>
+  <si>
+    <t>王子涵</t>
+  </si>
+  <si>
+    <t>张若曦</t>
+  </si>
+  <si>
+    <t>刘子琪</t>
+  </si>
+  <si>
+    <t>周子豪</t>
+  </si>
+  <si>
+    <t>郑乐瑶</t>
+  </si>
+  <si>
+    <t>林俊杰</t>
+  </si>
+  <si>
+    <t>郭静怡</t>
+  </si>
+  <si>
+    <t>唐雅琴</t>
+  </si>
+  <si>
+    <t>沈心怡</t>
+  </si>
+  <si>
+    <t>宋佳琪</t>
+  </si>
+  <si>
+    <t>欧阳雪儿</t>
+  </si>
+  <si>
+    <t>慕容婉儿</t>
+  </si>
+  <si>
+    <t>令狐嫣然</t>
+  </si>
+  <si>
+    <t>李慕紫</t>
+  </si>
+  <si>
+    <t>王小萌</t>
+  </si>
+  <si>
+    <t>张一辰</t>
+  </si>
+  <si>
+    <t>刘雨欣</t>
+  </si>
+  <si>
+    <t>赵子龙</t>
+  </si>
+  <si>
+    <t>陈小星</t>
+  </si>
+  <si>
+    <t>王浩然</t>
+  </si>
+  <si>
+    <t>周若曦</t>
+  </si>
+  <si>
+    <t>吴子骞</t>
+  </si>
+  <si>
+    <t>郑乐彤</t>
+  </si>
+  <si>
+    <t>林晨曦</t>
+  </si>
+  <si>
+    <t>郭雅琪</t>
+  </si>
+  <si>
+    <t>唐艺昕</t>
+  </si>
+  <si>
+    <t>沈佳琦</t>
+  </si>
+  <si>
+    <t>宋佳韵</t>
+  </si>
+  <si>
+    <t>欧阳雨桐</t>
+  </si>
+  <si>
+    <t>慕容晴雪</t>
+  </si>
+  <si>
+    <t>上官婉儿</t>
+  </si>
+  <si>
+    <t>司马相如</t>
+  </si>
+  <si>
+    <t>诸葛青云</t>
+  </si>
+  <si>
+    <t>东方不败</t>
+  </si>
+  <si>
+    <t>西门飘雪</t>
+  </si>
+  <si>
+    <t>独孤一鹤</t>
+  </si>
+  <si>
+    <t>李清风扬</t>
+  </si>
+  <si>
+    <t>王子涵月</t>
+  </si>
+  <si>
+    <t>张若曦晨</t>
+  </si>
+  <si>
+    <t>刘雨桐菲</t>
+  </si>
+  <si>
+    <t>赵梦瑶琳</t>
+  </si>
+  <si>
+    <t>陈思远航</t>
+  </si>
+  <si>
+    <t>王晓晨露</t>
+  </si>
+  <si>
+    <t>周子豪杰</t>
+  </si>
+  <si>
+    <t>吴佳怡然</t>
+  </si>
+  <si>
+    <t>郑乐瑶华</t>
+  </si>
+  <si>
+    <t>林俊杰瑞</t>
+  </si>
+  <si>
+    <t>郭静怡宁</t>
+  </si>
+  <si>
+    <t>唐雅琴韵</t>
+  </si>
+  <si>
+    <t>沈心怡然</t>
+  </si>
+  <si>
+    <t>宋佳琪瑶</t>
   </si>
 </sst>
 </file>
@@ -834,9 +1089,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1366,1295 +1624,4505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G56"/>
-  <sheetFormatPr defaultColWidth="8.609375" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <dimension ref="A1:I155"/>
+  <sheetFormatPr defaultColWidth="8.609375" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="1" max="16384" width="8.609375" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1">
         <v>202601</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2">
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>85</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>92</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>78</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
+      <c r="H2" s="1">
+        <v>67</v>
+      </c>
+      <c r="I2" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1">
         <v>202602</v>
       </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3">
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1">
         <v>2</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>76</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>68</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>82</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
+      <c r="H3" s="1">
+        <v>89</v>
+      </c>
+      <c r="I3" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1">
         <v>202603</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4">
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1">
         <v>1</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>90</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>88</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>95</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
+      <c r="H4" s="1">
+        <v>55</v>
+      </c>
+      <c r="I4" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1">
         <v>202604</v>
       </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5">
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1">
         <v>3</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>59</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>62</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>55</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
+      <c r="H5" s="1">
+        <v>84</v>
+      </c>
+      <c r="I5" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1">
         <v>202605</v>
       </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6">
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1">
         <v>4</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>88</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>95</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>91</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
+      <c r="H6" s="1">
+        <v>71</v>
+      </c>
+      <c r="I6" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1">
         <v>202606</v>
       </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7">
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1">
         <v>2</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>72</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>85</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>88</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
+      <c r="H7" s="1">
+        <v>72</v>
+      </c>
+      <c r="I7" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1">
         <v>202607</v>
       </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8">
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="1">
         <v>4</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>96</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>80</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>56</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
+      <c r="H8" s="1">
+        <v>56</v>
+      </c>
+      <c r="I8" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1">
         <v>202608</v>
       </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9">
+      <c r="B9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="1">
         <v>3</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>59</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>79</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>95</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
+      <c r="H9" s="1">
+        <v>47</v>
+      </c>
+      <c r="I9" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1">
         <v>202609</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1">
+        <v>55</v>
+      </c>
+      <c r="F10" s="1">
+        <v>94</v>
+      </c>
+      <c r="G10" s="1">
+        <v>71</v>
+      </c>
+      <c r="H10" s="1">
+        <v>50</v>
+      </c>
+      <c r="I10" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1">
+        <v>202610</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="1">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1">
+        <v>51</v>
+      </c>
+      <c r="F11" s="1">
+        <v>87</v>
+      </c>
+      <c r="G11" s="1">
+        <v>56</v>
+      </c>
+      <c r="H11" s="1">
+        <v>51</v>
+      </c>
+      <c r="I11" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="1">
+        <v>202611</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="1">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1">
+        <v>96</v>
+      </c>
+      <c r="F12" s="1">
+        <v>94</v>
+      </c>
+      <c r="G12" s="1">
+        <v>82</v>
+      </c>
+      <c r="H12" s="1">
+        <v>65</v>
+      </c>
+      <c r="I12" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="1">
+        <v>202612</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="1">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1">
+        <v>61</v>
+      </c>
+      <c r="F13" s="1">
+        <v>64</v>
+      </c>
+      <c r="G13" s="1">
+        <v>76</v>
+      </c>
+      <c r="H13" s="1">
+        <v>72</v>
+      </c>
+      <c r="I13" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="1">
+        <v>202613</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="1">
+        <v>2</v>
+      </c>
+      <c r="E14" s="1">
+        <v>63</v>
+      </c>
+      <c r="F14" s="1">
+        <v>82</v>
+      </c>
+      <c r="G14" s="1">
+        <v>70</v>
+      </c>
+      <c r="H14" s="1">
+        <v>84</v>
+      </c>
+      <c r="I14" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="1">
+        <v>202614</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="1">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1">
+        <v>61</v>
+      </c>
+      <c r="F15" s="1">
+        <v>51</v>
+      </c>
+      <c r="G15" s="1">
+        <v>97</v>
+      </c>
+      <c r="H15" s="1">
+        <v>54</v>
+      </c>
+      <c r="I15" s="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="1">
+        <v>202615</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>58</v>
+      </c>
+      <c r="F16" s="1">
+        <v>79</v>
+      </c>
+      <c r="G16" s="1">
+        <v>63</v>
+      </c>
+      <c r="H16" s="1">
+        <v>87</v>
+      </c>
+      <c r="I16" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="1">
+        <v>202616</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>56</v>
+      </c>
+      <c r="F17" s="1">
+        <v>45</v>
+      </c>
+      <c r="G17" s="1">
+        <v>63</v>
+      </c>
+      <c r="H17" s="1">
+        <v>73</v>
+      </c>
+      <c r="I17" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="1">
+        <v>202617</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>80</v>
+      </c>
+      <c r="F18" s="1">
+        <v>93</v>
+      </c>
+      <c r="G18" s="1">
+        <v>79</v>
+      </c>
+      <c r="H18" s="1">
+        <v>68</v>
+      </c>
+      <c r="I18" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="1">
+        <v>202618</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="1">
+        <v>5</v>
+      </c>
+      <c r="E19" s="1">
+        <v>56</v>
+      </c>
+      <c r="F19" s="1">
+        <v>91</v>
+      </c>
+      <c r="G19" s="1">
+        <v>96</v>
+      </c>
+      <c r="H19" s="1">
+        <v>63</v>
+      </c>
+      <c r="I19" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="1">
+        <v>202619</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="1">
+        <v>3</v>
+      </c>
+      <c r="E20" s="1">
+        <v>42</v>
+      </c>
+      <c r="F20" s="1">
+        <v>65</v>
+      </c>
+      <c r="G20" s="1">
+        <v>63</v>
+      </c>
+      <c r="H20" s="1">
+        <v>90</v>
+      </c>
+      <c r="I20" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="1">
+        <v>202620</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1">
+        <v>83</v>
+      </c>
+      <c r="F21" s="1">
+        <v>99</v>
+      </c>
+      <c r="G21" s="1">
+        <v>67</v>
+      </c>
+      <c r="H21" s="1">
+        <v>47</v>
+      </c>
+      <c r="I21" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="1">
+        <v>202621</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="1">
+        <v>4</v>
+      </c>
+      <c r="E22" s="1">
+        <v>72</v>
+      </c>
+      <c r="F22" s="1">
+        <v>81</v>
+      </c>
+      <c r="G22" s="1">
+        <v>90</v>
+      </c>
+      <c r="H22" s="1">
+        <v>56</v>
+      </c>
+      <c r="I22" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="1">
+        <v>202622</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="1">
+        <v>4</v>
+      </c>
+      <c r="E23" s="1">
+        <v>89</v>
+      </c>
+      <c r="F23" s="1">
+        <v>93</v>
+      </c>
+      <c r="G23" s="1">
+        <v>75</v>
+      </c>
+      <c r="H23" s="1">
+        <v>80</v>
+      </c>
+      <c r="I23" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="1">
+        <v>202623</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="1">
+        <v>5</v>
+      </c>
+      <c r="E24" s="1">
+        <v>73</v>
+      </c>
+      <c r="F24" s="1">
+        <v>65</v>
+      </c>
+      <c r="G24" s="1">
+        <v>59</v>
+      </c>
+      <c r="H24" s="1">
+        <v>96</v>
+      </c>
+      <c r="I24" s="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="1">
+        <v>202624</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="1">
+        <v>4</v>
+      </c>
+      <c r="E25" s="1">
+        <v>53</v>
+      </c>
+      <c r="F25" s="1">
+        <v>72</v>
+      </c>
+      <c r="G25" s="1">
+        <v>70</v>
+      </c>
+      <c r="H25" s="1">
+        <v>63</v>
+      </c>
+      <c r="I25" s="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="1">
+        <v>202625</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="1">
+        <v>4</v>
+      </c>
+      <c r="E26" s="1">
+        <v>95</v>
+      </c>
+      <c r="F26" s="1">
+        <v>25</v>
+      </c>
+      <c r="G26" s="1">
+        <v>87</v>
+      </c>
+      <c r="H26" s="1">
+        <v>78</v>
+      </c>
+      <c r="I26" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="1">
+        <v>202626</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2</v>
+      </c>
+      <c r="E27" s="1">
+        <v>62</v>
+      </c>
+      <c r="F27" s="1">
+        <v>82</v>
+      </c>
+      <c r="G27" s="1">
+        <v>54</v>
+      </c>
+      <c r="H27" s="1">
+        <v>50</v>
+      </c>
+      <c r="I27" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="1">
+        <v>202627</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="1">
+        <v>3</v>
+      </c>
+      <c r="E28" s="1">
+        <v>70</v>
+      </c>
+      <c r="F28" s="1">
+        <v>63</v>
+      </c>
+      <c r="G28" s="1">
+        <v>67</v>
+      </c>
+      <c r="H28" s="1">
+        <v>52</v>
+      </c>
+      <c r="I28" s="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="1">
+        <v>202628</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="1">
+        <v>3</v>
+      </c>
+      <c r="E29" s="1">
+        <v>77</v>
+      </c>
+      <c r="F29" s="1">
+        <v>49</v>
+      </c>
+      <c r="G29" s="1">
+        <v>75</v>
+      </c>
+      <c r="H29" s="1">
+        <v>41</v>
+      </c>
+      <c r="I29" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="1">
+        <v>202629</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="1">
+        <v>3</v>
+      </c>
+      <c r="E30" s="1">
+        <v>52</v>
+      </c>
+      <c r="F30" s="1">
+        <v>70</v>
+      </c>
+      <c r="G30" s="1">
+        <v>41</v>
+      </c>
+      <c r="H30" s="1">
+        <v>90</v>
+      </c>
+      <c r="I30" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="1">
+        <v>202630</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="1">
+        <v>3</v>
+      </c>
+      <c r="E31" s="1">
+        <v>52</v>
+      </c>
+      <c r="F31" s="1">
+        <v>61</v>
+      </c>
+      <c r="G31" s="1">
+        <v>52</v>
+      </c>
+      <c r="H31" s="1">
+        <v>76</v>
+      </c>
+      <c r="I31" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="1">
+        <v>202631</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2</v>
+      </c>
+      <c r="E32" s="1">
+        <v>93</v>
+      </c>
+      <c r="F32" s="1">
+        <v>51</v>
+      </c>
+      <c r="G32" s="1">
+        <v>71</v>
+      </c>
+      <c r="H32" s="1">
+        <v>54</v>
+      </c>
+      <c r="I32" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="1">
+        <v>202632</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="1">
+        <v>5</v>
+      </c>
+      <c r="E33" s="1">
+        <v>70</v>
+      </c>
+      <c r="F33" s="1">
+        <v>74</v>
+      </c>
+      <c r="G33" s="1">
+        <v>62</v>
+      </c>
+      <c r="H33" s="1">
+        <v>42</v>
+      </c>
+      <c r="I33" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="1">
+        <v>202633</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2</v>
+      </c>
+      <c r="E34" s="1">
+        <v>57</v>
+      </c>
+      <c r="F34" s="1">
+        <v>97</v>
+      </c>
+      <c r="G34" s="1">
+        <v>52</v>
+      </c>
+      <c r="H34" s="1">
+        <v>51</v>
+      </c>
+      <c r="I34" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="1">
+        <v>202634</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2</v>
+      </c>
+      <c r="E35" s="1">
+        <v>50</v>
+      </c>
+      <c r="F35" s="1">
+        <v>52</v>
+      </c>
+      <c r="G35" s="1">
+        <v>44</v>
+      </c>
+      <c r="H35" s="1">
+        <v>88</v>
+      </c>
+      <c r="I35" s="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="1">
+        <v>202635</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" s="1">
+        <v>3</v>
+      </c>
+      <c r="E36" s="1">
+        <v>60</v>
+      </c>
+      <c r="F36" s="1">
+        <v>94</v>
+      </c>
+      <c r="G36" s="1">
+        <v>87</v>
+      </c>
+      <c r="H36" s="1">
+        <v>66</v>
+      </c>
+      <c r="I36" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="1">
+        <v>202636</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" s="1">
+        <v>4</v>
+      </c>
+      <c r="E37" s="1">
+        <v>89</v>
+      </c>
+      <c r="F37" s="1">
+        <v>59</v>
+      </c>
+      <c r="G37" s="1">
+        <v>54</v>
+      </c>
+      <c r="H37" s="1">
+        <v>75</v>
+      </c>
+      <c r="I37" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="1">
+        <v>202637</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1">
+        <v>96</v>
+      </c>
+      <c r="F38" s="1">
+        <v>53</v>
+      </c>
+      <c r="G38" s="1">
+        <v>70</v>
+      </c>
+      <c r="H38" s="1">
+        <v>88</v>
+      </c>
+      <c r="I38" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="1">
+        <v>202638</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="1">
+        <v>2</v>
+      </c>
+      <c r="E39" s="1">
+        <v>49</v>
+      </c>
+      <c r="F39" s="1">
+        <v>20</v>
+      </c>
+      <c r="G39" s="1">
+        <v>49</v>
+      </c>
+      <c r="H39" s="1">
+        <v>65</v>
+      </c>
+      <c r="I39" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="1">
+        <v>202639</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" s="1">
+        <v>2</v>
+      </c>
+      <c r="E40" s="1">
+        <v>73</v>
+      </c>
+      <c r="F40" s="1">
+        <v>93</v>
+      </c>
+      <c r="G40" s="1">
+        <v>71</v>
+      </c>
+      <c r="H40" s="1">
+        <v>80</v>
+      </c>
+      <c r="I40" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="1">
+        <v>202640</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" s="1">
+        <v>2</v>
+      </c>
+      <c r="E41" s="1">
+        <v>56</v>
+      </c>
+      <c r="F41" s="1">
+        <v>95</v>
+      </c>
+      <c r="G41" s="1">
+        <v>72</v>
+      </c>
+      <c r="H41" s="1">
+        <v>47</v>
+      </c>
+      <c r="I41" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="1">
+        <v>202641</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1</v>
+      </c>
+      <c r="E42" s="1">
+        <v>92</v>
+      </c>
+      <c r="F42" s="1">
+        <v>95</v>
+      </c>
+      <c r="G42" s="1">
+        <v>75</v>
+      </c>
+      <c r="H42" s="1">
+        <v>41</v>
+      </c>
+      <c r="I42" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="1">
+        <v>202642</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1</v>
+      </c>
+      <c r="E43" s="1">
+        <v>53</v>
+      </c>
+      <c r="F43" s="1">
+        <v>72</v>
+      </c>
+      <c r="G43" s="1">
+        <v>71</v>
+      </c>
+      <c r="H43" s="1">
+        <v>57</v>
+      </c>
+      <c r="I43" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="1">
+        <v>202643</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1</v>
+      </c>
+      <c r="E44" s="1">
+        <v>58</v>
+      </c>
+      <c r="F44" s="1">
+        <v>86</v>
+      </c>
+      <c r="G44" s="1">
+        <v>69</v>
+      </c>
+      <c r="H44" s="1">
+        <v>97</v>
+      </c>
+      <c r="I44" s="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="1">
+        <v>202644</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="1">
+        <v>5</v>
+      </c>
+      <c r="E45" s="1">
+        <v>56</v>
+      </c>
+      <c r="F45" s="1">
+        <v>70</v>
+      </c>
+      <c r="G45" s="1">
+        <v>81</v>
+      </c>
+      <c r="H45" s="1">
+        <v>63</v>
+      </c>
+      <c r="I45" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="1">
+        <v>202645</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="1">
+        <v>5</v>
+      </c>
+      <c r="E46" s="1">
+        <v>95</v>
+      </c>
+      <c r="F46" s="1">
+        <v>78</v>
+      </c>
+      <c r="G46" s="1">
+        <v>74</v>
+      </c>
+      <c r="H46" s="1">
+        <v>52</v>
+      </c>
+      <c r="I46" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="1">
+        <v>202646</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" s="1">
+        <v>3</v>
+      </c>
+      <c r="E47" s="1">
+        <v>94</v>
+      </c>
+      <c r="F47" s="1">
+        <v>95</v>
+      </c>
+      <c r="G47" s="1">
+        <v>74</v>
+      </c>
+      <c r="H47" s="1">
+        <v>42</v>
+      </c>
+      <c r="I47" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="1">
+        <v>202647</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" s="1">
+        <v>3</v>
+      </c>
+      <c r="E48" s="1">
+        <v>46</v>
+      </c>
+      <c r="F48" s="1">
+        <v>47</v>
+      </c>
+      <c r="G48" s="1">
+        <v>93</v>
+      </c>
+      <c r="H48" s="1">
+        <v>55</v>
+      </c>
+      <c r="I48" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="1">
+        <v>202648</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" s="1">
+        <v>3</v>
+      </c>
+      <c r="E49" s="1">
+        <v>77</v>
+      </c>
+      <c r="F49" s="1">
+        <v>56</v>
+      </c>
+      <c r="G49" s="1">
+        <v>74</v>
+      </c>
+      <c r="H49" s="1">
+        <v>53</v>
+      </c>
+      <c r="I49" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="1">
+        <v>202649</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="1">
+        <v>1</v>
+      </c>
+      <c r="E50" s="1">
+        <v>93</v>
+      </c>
+      <c r="F50" s="1">
+        <v>56</v>
+      </c>
+      <c r="G50" s="1">
+        <v>92</v>
+      </c>
+      <c r="H50" s="1">
+        <v>47</v>
+      </c>
+      <c r="I50" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="1">
+        <v>202650</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" s="1">
+        <v>4</v>
+      </c>
+      <c r="E51" s="1">
+        <v>89</v>
+      </c>
+      <c r="F51" s="1">
+        <v>50</v>
+      </c>
+      <c r="G51" s="1">
+        <v>89</v>
+      </c>
+      <c r="H51" s="1">
+        <v>100</v>
+      </c>
+      <c r="I51" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="1">
+        <v>202651</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="1">
+        <v>2</v>
+      </c>
+      <c r="E52" s="1">
+        <v>75</v>
+      </c>
+      <c r="F52" s="1">
+        <v>72</v>
+      </c>
+      <c r="G52" s="1">
+        <v>61</v>
+      </c>
+      <c r="H52" s="1">
+        <v>42</v>
+      </c>
+      <c r="I52" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="1">
+        <v>202652</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="1">
+        <v>3</v>
+      </c>
+      <c r="E53" s="1">
+        <v>60</v>
+      </c>
+      <c r="F53" s="1">
+        <v>89</v>
+      </c>
+      <c r="G53" s="1">
+        <v>52</v>
+      </c>
+      <c r="H53" s="1">
+        <v>92</v>
+      </c>
+      <c r="I53" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="1">
+        <v>202653</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" s="1">
+        <v>4</v>
+      </c>
+      <c r="E54" s="1">
+        <v>76</v>
+      </c>
+      <c r="F54" s="1">
+        <v>100</v>
+      </c>
+      <c r="G54" s="1">
+        <v>67</v>
+      </c>
+      <c r="H54" s="1">
+        <v>97</v>
+      </c>
+      <c r="I54" s="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="1">
+        <v>202654</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="1">
+        <v>4</v>
+      </c>
+      <c r="E55" s="1">
+        <v>81</v>
+      </c>
+      <c r="F55" s="1">
+        <v>53</v>
+      </c>
+      <c r="G55" s="1">
+        <v>85</v>
+      </c>
+      <c r="H55" s="1">
+        <v>54</v>
+      </c>
+      <c r="I55" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="1">
+        <v>202655</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" s="1">
+        <v>1</v>
+      </c>
+      <c r="E56" s="1">
+        <v>41</v>
+      </c>
+      <c r="F56" s="1">
+        <v>98</v>
+      </c>
+      <c r="G56" s="1">
+        <v>70</v>
+      </c>
+      <c r="H56" s="1">
+        <v>81</v>
+      </c>
+      <c r="I56" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="1">
+        <v>202656</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="1">
+        <v>4</v>
+      </c>
+      <c r="E57" s="1">
+        <v>44</v>
+      </c>
+      <c r="F57" s="1">
+        <v>80</v>
+      </c>
+      <c r="G57" s="1">
+        <v>53</v>
+      </c>
+      <c r="H57" s="1">
+        <v>53</v>
+      </c>
+      <c r="I57" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="1">
+        <v>202657</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" s="1">
+        <v>1</v>
+      </c>
+      <c r="E58" s="1">
+        <v>66</v>
+      </c>
+      <c r="F58" s="1">
+        <v>94</v>
+      </c>
+      <c r="G58" s="1">
+        <v>52</v>
+      </c>
+      <c r="H58" s="1">
+        <v>70</v>
+      </c>
+      <c r="I58" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="1">
+        <v>202658</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" s="1">
+        <v>5</v>
+      </c>
+      <c r="E59" s="1">
+        <v>72</v>
+      </c>
+      <c r="F59" s="1">
+        <v>79</v>
+      </c>
+      <c r="G59" s="1">
+        <v>93</v>
+      </c>
+      <c r="H59" s="1">
+        <v>82</v>
+      </c>
+      <c r="I59" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="1">
+        <v>202659</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" s="1">
+        <v>1</v>
+      </c>
+      <c r="E60" s="1">
+        <v>48</v>
+      </c>
+      <c r="F60" s="1">
+        <v>46</v>
+      </c>
+      <c r="G60" s="1">
+        <v>71</v>
+      </c>
+      <c r="H60" s="1">
+        <v>98</v>
+      </c>
+      <c r="I60" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="1">
+        <v>202660</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" s="1">
+        <v>3</v>
+      </c>
+      <c r="E61" s="1">
+        <v>40</v>
+      </c>
+      <c r="F61" s="1">
+        <v>42</v>
+      </c>
+      <c r="G61" s="1">
+        <v>73</v>
+      </c>
+      <c r="H61" s="1">
+        <v>94</v>
+      </c>
+      <c r="I61" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="1">
+        <v>202661</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" s="1">
+        <v>2</v>
+      </c>
+      <c r="E62" s="1">
+        <v>100</v>
+      </c>
+      <c r="F62" s="1">
+        <v>46</v>
+      </c>
+      <c r="G62" s="1">
+        <v>80</v>
+      </c>
+      <c r="H62" s="1">
+        <v>59</v>
+      </c>
+      <c r="I62" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="1">
+        <v>202662</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D63" s="1">
+        <v>4</v>
+      </c>
+      <c r="E63" s="1">
+        <v>83</v>
+      </c>
+      <c r="F63" s="1">
+        <v>56</v>
+      </c>
+      <c r="G63" s="1">
+        <v>72</v>
+      </c>
+      <c r="H63" s="1">
+        <v>95</v>
+      </c>
+      <c r="I63" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" s="1">
+        <v>202663</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" s="1">
+        <v>4</v>
+      </c>
+      <c r="E64" s="1">
+        <v>86</v>
+      </c>
+      <c r="F64" s="1">
+        <v>60</v>
+      </c>
+      <c r="G64" s="1">
+        <v>73</v>
+      </c>
+      <c r="H64" s="1">
+        <v>78</v>
+      </c>
+      <c r="I64" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" s="1">
+        <v>202664</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65" s="1">
+        <v>2</v>
+      </c>
+      <c r="E65" s="1">
+        <v>80</v>
+      </c>
+      <c r="F65" s="1">
+        <v>75</v>
+      </c>
+      <c r="G65" s="1">
+        <v>73</v>
+      </c>
+      <c r="H65" s="1">
+        <v>98</v>
+      </c>
+      <c r="I65" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" s="1">
+        <v>202665</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D66" s="1">
+        <v>2</v>
+      </c>
+      <c r="E66" s="1">
+        <v>47</v>
+      </c>
+      <c r="F66" s="1">
+        <v>77</v>
+      </c>
+      <c r="G66" s="1">
+        <v>88</v>
+      </c>
+      <c r="H66" s="1">
+        <v>47</v>
+      </c>
+      <c r="I66" s="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" s="1">
+        <v>202666</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D67" s="1">
+        <v>5</v>
+      </c>
+      <c r="E67" s="1">
+        <v>41</v>
+      </c>
+      <c r="F67" s="1">
+        <v>69</v>
+      </c>
+      <c r="G67" s="1">
+        <v>52</v>
+      </c>
+      <c r="H67" s="1">
+        <v>64</v>
+      </c>
+      <c r="I67" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" s="1">
+        <v>202667</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68" s="1">
+        <v>4</v>
+      </c>
+      <c r="E68" s="1">
+        <v>93</v>
+      </c>
+      <c r="F68" s="1">
+        <v>43</v>
+      </c>
+      <c r="G68" s="1">
+        <v>90</v>
+      </c>
+      <c r="H68" s="1">
+        <v>78</v>
+      </c>
+      <c r="I68" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" s="1">
+        <v>202668</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" s="1">
+        <v>1</v>
+      </c>
+      <c r="E69" s="1">
+        <v>67</v>
+      </c>
+      <c r="F69" s="1">
+        <v>96</v>
+      </c>
+      <c r="G69" s="1">
+        <v>57</v>
+      </c>
+      <c r="H69" s="1">
+        <v>97</v>
+      </c>
+      <c r="I69" s="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" s="1">
+        <v>202669</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70" s="1">
+        <v>5</v>
+      </c>
+      <c r="E70" s="1">
+        <v>47</v>
+      </c>
+      <c r="F70" s="1">
+        <v>95</v>
+      </c>
+      <c r="G70" s="1">
+        <v>91</v>
+      </c>
+      <c r="H70" s="1">
+        <v>43</v>
+      </c>
+      <c r="I70" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" s="1">
+        <v>202670</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D71" s="1">
+        <v>1</v>
+      </c>
+      <c r="E71" s="1">
+        <v>56</v>
+      </c>
+      <c r="F71" s="1">
+        <v>53</v>
+      </c>
+      <c r="G71" s="1">
+        <v>88</v>
+      </c>
+      <c r="H71" s="1">
+        <v>100</v>
+      </c>
+      <c r="I71" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" s="1">
+        <v>202671</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" s="1">
+        <v>4</v>
+      </c>
+      <c r="E72" s="1">
+        <v>59</v>
+      </c>
+      <c r="F72" s="1">
+        <v>47</v>
+      </c>
+      <c r="G72" s="1">
+        <v>51</v>
+      </c>
+      <c r="H72" s="1">
+        <v>75</v>
+      </c>
+      <c r="I72" s="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" s="1">
+        <v>202672</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D73" s="1">
+        <v>2</v>
+      </c>
+      <c r="E73" s="1">
+        <v>84</v>
+      </c>
+      <c r="F73" s="1">
+        <v>79</v>
+      </c>
+      <c r="G73" s="1">
+        <v>84</v>
+      </c>
+      <c r="H73" s="1">
+        <v>56</v>
+      </c>
+      <c r="I73" s="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" s="1">
+        <v>202673</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D74" s="1">
+        <v>2</v>
+      </c>
+      <c r="E74" s="1">
+        <v>60</v>
+      </c>
+      <c r="F74" s="1">
+        <v>90</v>
+      </c>
+      <c r="G74" s="1">
+        <v>43</v>
+      </c>
+      <c r="H74" s="1">
+        <v>90</v>
+      </c>
+      <c r="I74" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" s="1">
+        <v>202674</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75" s="1">
+        <v>2</v>
+      </c>
+      <c r="E75" s="1">
+        <v>100</v>
+      </c>
+      <c r="F75" s="1">
+        <v>79</v>
+      </c>
+      <c r="G75" s="1">
+        <v>49</v>
+      </c>
+      <c r="H75" s="1">
+        <v>62</v>
+      </c>
+      <c r="I75" s="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" s="1">
+        <v>202675</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76" s="1">
+        <v>5</v>
+      </c>
+      <c r="E76" s="1">
+        <v>98</v>
+      </c>
+      <c r="F76" s="1">
+        <v>91</v>
+      </c>
+      <c r="G76" s="1">
+        <v>75</v>
+      </c>
+      <c r="H76" s="1">
+        <v>74</v>
+      </c>
+      <c r="I76" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" s="1">
+        <v>202676</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10">
+      <c r="C77" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D77" s="1">
         <v>3</v>
       </c>
-      <c r="E10">
+      <c r="E77" s="1">
+        <v>72</v>
+      </c>
+      <c r="F77" s="1">
         <v>55</v>
       </c>
-      <c r="F10">
+      <c r="G77" s="1">
+        <v>56</v>
+      </c>
+      <c r="H77" s="1">
+        <v>71</v>
+      </c>
+      <c r="I77" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" s="1">
+        <v>202677</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78" s="1">
+        <v>2</v>
+      </c>
+      <c r="E78" s="1">
+        <v>67</v>
+      </c>
+      <c r="F78" s="1">
+        <v>49</v>
+      </c>
+      <c r="G78" s="1">
+        <v>68</v>
+      </c>
+      <c r="H78" s="1">
+        <v>42</v>
+      </c>
+      <c r="I78" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" s="1">
+        <v>202678</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D79" s="1">
+        <v>3</v>
+      </c>
+      <c r="E79" s="1">
+        <v>93</v>
+      </c>
+      <c r="F79" s="1">
+        <v>69</v>
+      </c>
+      <c r="G79" s="1">
+        <v>57</v>
+      </c>
+      <c r="H79" s="1">
+        <v>64</v>
+      </c>
+      <c r="I79" s="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" s="1">
+        <v>202679</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" s="1">
+        <v>2</v>
+      </c>
+      <c r="E80" s="1">
+        <v>44</v>
+      </c>
+      <c r="F80" s="1">
+        <v>87</v>
+      </c>
+      <c r="G80" s="1">
+        <v>71</v>
+      </c>
+      <c r="H80" s="1">
+        <v>75</v>
+      </c>
+      <c r="I80" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" s="1">
+        <v>202680</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D81" s="1">
+        <v>4</v>
+      </c>
+      <c r="E81" s="1">
+        <v>62</v>
+      </c>
+      <c r="F81" s="1">
+        <v>70</v>
+      </c>
+      <c r="G81" s="1">
+        <v>96</v>
+      </c>
+      <c r="H81" s="1">
+        <v>70</v>
+      </c>
+      <c r="I81" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" s="1">
+        <v>202681</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82" s="1">
+        <v>5</v>
+      </c>
+      <c r="E82" s="1">
+        <v>47</v>
+      </c>
+      <c r="F82" s="1">
+        <v>95</v>
+      </c>
+      <c r="G82" s="1">
+        <v>75</v>
+      </c>
+      <c r="H82" s="1">
+        <v>54</v>
+      </c>
+      <c r="I82" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" s="1">
+        <v>202682</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D83" s="1">
+        <v>4</v>
+      </c>
+      <c r="E83" s="1">
+        <v>55</v>
+      </c>
+      <c r="F83" s="1">
+        <v>82</v>
+      </c>
+      <c r="G83" s="1">
+        <v>87</v>
+      </c>
+      <c r="H83" s="1">
+        <v>83</v>
+      </c>
+      <c r="I83" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" s="1">
+        <v>202683</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D84" s="1">
+        <v>1</v>
+      </c>
+      <c r="E84" s="1">
+        <v>54</v>
+      </c>
+      <c r="F84" s="1">
+        <v>40</v>
+      </c>
+      <c r="G84" s="1">
+        <v>46</v>
+      </c>
+      <c r="H84" s="1">
+        <v>87</v>
+      </c>
+      <c r="I84" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" s="1">
+        <v>202684</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D85" s="1">
+        <v>1</v>
+      </c>
+      <c r="E85" s="1">
+        <v>47</v>
+      </c>
+      <c r="F85" s="1">
+        <v>46</v>
+      </c>
+      <c r="G85" s="1">
+        <v>55</v>
+      </c>
+      <c r="H85" s="1">
+        <v>85</v>
+      </c>
+      <c r="I85" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" s="1">
+        <v>202685</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D86" s="1">
+        <v>3</v>
+      </c>
+      <c r="E86" s="1">
+        <v>56</v>
+      </c>
+      <c r="F86" s="1">
+        <v>42</v>
+      </c>
+      <c r="G86" s="1">
+        <v>43</v>
+      </c>
+      <c r="H86" s="1">
+        <v>46</v>
+      </c>
+      <c r="I86" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" s="1">
+        <v>202686</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D87" s="1">
+        <v>4</v>
+      </c>
+      <c r="E87" s="1">
+        <v>47</v>
+      </c>
+      <c r="F87" s="1">
+        <v>66</v>
+      </c>
+      <c r="G87" s="1">
+        <v>74</v>
+      </c>
+      <c r="H87" s="1">
+        <v>82</v>
+      </c>
+      <c r="I87" s="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="1">
+        <v>202687</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D88" s="1">
+        <v>2</v>
+      </c>
+      <c r="E88" s="1">
+        <v>55</v>
+      </c>
+      <c r="F88" s="1">
+        <v>67</v>
+      </c>
+      <c r="G88" s="1">
+        <v>56</v>
+      </c>
+      <c r="H88" s="1">
+        <v>84</v>
+      </c>
+      <c r="I88" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" s="1">
+        <v>202688</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D89" s="1">
+        <v>4</v>
+      </c>
+      <c r="E89" s="1">
+        <v>44</v>
+      </c>
+      <c r="F89" s="1">
+        <v>80</v>
+      </c>
+      <c r="G89" s="1">
+        <v>66</v>
+      </c>
+      <c r="H89" s="1">
+        <v>56</v>
+      </c>
+      <c r="I89" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" s="1">
+        <v>202689</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90" s="1">
+        <v>2</v>
+      </c>
+      <c r="E90" s="1">
+        <v>47</v>
+      </c>
+      <c r="F90" s="1">
+        <v>44</v>
+      </c>
+      <c r="G90" s="1">
+        <v>45</v>
+      </c>
+      <c r="H90" s="1">
         <v>94</v>
       </c>
-      <c r="G10">
+      <c r="I90" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" s="1">
+        <v>202690</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" s="1">
+        <v>4</v>
+      </c>
+      <c r="E91" s="1">
+        <v>55</v>
+      </c>
+      <c r="F91" s="1">
+        <v>75</v>
+      </c>
+      <c r="G91" s="1">
+        <v>50</v>
+      </c>
+      <c r="H91" s="1">
+        <v>95</v>
+      </c>
+      <c r="I91" s="1">
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>202610</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11">
+    <row r="92" spans="1:9">
+      <c r="A92" s="1">
+        <v>202691</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D92" s="1">
+        <v>4</v>
+      </c>
+      <c r="E92" s="1">
+        <v>45</v>
+      </c>
+      <c r="F92" s="1">
+        <v>95</v>
+      </c>
+      <c r="G92" s="1">
+        <v>40</v>
+      </c>
+      <c r="H92" s="1">
+        <v>93</v>
+      </c>
+      <c r="I92" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" s="1">
+        <v>202692</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93" s="1">
+        <v>2</v>
+      </c>
+      <c r="E93" s="1">
+        <v>92</v>
+      </c>
+      <c r="F93" s="1">
+        <v>46</v>
+      </c>
+      <c r="G93" s="1">
+        <v>78</v>
+      </c>
+      <c r="H93" s="1">
+        <v>62</v>
+      </c>
+      <c r="I93" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" s="1">
+        <v>202693</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D94" s="1">
+        <v>4</v>
+      </c>
+      <c r="E94" s="1">
+        <v>52</v>
+      </c>
+      <c r="F94" s="1">
+        <v>40</v>
+      </c>
+      <c r="G94" s="1">
+        <v>80</v>
+      </c>
+      <c r="H94" s="1">
+        <v>86</v>
+      </c>
+      <c r="I94" s="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" s="1">
+        <v>202694</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95" s="1">
+        <v>2</v>
+      </c>
+      <c r="E95" s="1">
+        <v>48</v>
+      </c>
+      <c r="F95" s="1">
+        <v>59</v>
+      </c>
+      <c r="G95" s="1">
+        <v>84</v>
+      </c>
+      <c r="H95" s="1">
+        <v>55</v>
+      </c>
+      <c r="I95" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" s="1">
+        <v>202695</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D96" s="1">
+        <v>2</v>
+      </c>
+      <c r="E96" s="1">
+        <v>75</v>
+      </c>
+      <c r="F96" s="1">
+        <v>65</v>
+      </c>
+      <c r="G96" s="1">
+        <v>42</v>
+      </c>
+      <c r="H96" s="1">
+        <v>97</v>
+      </c>
+      <c r="I96" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" s="1">
+        <v>202696</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D97" s="1">
+        <v>1</v>
+      </c>
+      <c r="E97" s="1">
+        <v>56</v>
+      </c>
+      <c r="F97" s="1">
+        <v>40</v>
+      </c>
+      <c r="G97" s="1">
+        <v>54</v>
+      </c>
+      <c r="H97" s="1">
+        <v>51</v>
+      </c>
+      <c r="I97" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" s="1">
+        <v>202697</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98" s="1">
+        <v>4</v>
+      </c>
+      <c r="E98" s="1">
+        <v>83</v>
+      </c>
+      <c r="F98" s="1">
+        <v>68</v>
+      </c>
+      <c r="G98" s="1">
+        <v>89</v>
+      </c>
+      <c r="H98" s="1">
+        <v>55</v>
+      </c>
+      <c r="I98" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" s="1">
+        <v>202698</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D99" s="1">
         <v>5</v>
       </c>
-      <c r="E11">
+      <c r="E99" s="1">
+        <v>83</v>
+      </c>
+      <c r="F99" s="1">
+        <v>92</v>
+      </c>
+      <c r="G99" s="1">
+        <v>91</v>
+      </c>
+      <c r="H99" s="1">
+        <v>83</v>
+      </c>
+      <c r="I99" s="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" s="1">
+        <v>202699</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D100" s="1">
+        <v>4</v>
+      </c>
+      <c r="E100" s="1">
+        <v>49</v>
+      </c>
+      <c r="F100" s="1">
+        <v>91</v>
+      </c>
+      <c r="G100" s="1">
+        <v>69</v>
+      </c>
+      <c r="H100" s="1">
         <v>51</v>
       </c>
-      <c r="F11">
+      <c r="I100" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" s="1">
+        <v>202700</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101" s="1">
+        <v>4</v>
+      </c>
+      <c r="E101" s="1">
+        <v>50</v>
+      </c>
+      <c r="F101" s="1">
+        <v>67</v>
+      </c>
+      <c r="G101" s="1">
+        <v>72</v>
+      </c>
+      <c r="H101" s="1">
+        <v>68</v>
+      </c>
+      <c r="I101" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" s="1">
+        <v>202701</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" s="1">
+        <v>5</v>
+      </c>
+      <c r="E102" s="1">
+        <v>90</v>
+      </c>
+      <c r="F102" s="1">
+        <v>54</v>
+      </c>
+      <c r="G102" s="1">
+        <v>92</v>
+      </c>
+      <c r="H102" s="1">
         <v>87</v>
       </c>
-      <c r="G11">
+      <c r="I102" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" s="1">
+        <v>202702</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D103" s="1">
+        <v>4</v>
+      </c>
+      <c r="E103" s="1">
+        <v>71</v>
+      </c>
+      <c r="F103" s="1">
+        <v>42</v>
+      </c>
+      <c r="G103" s="1">
+        <v>44</v>
+      </c>
+      <c r="H103" s="1">
+        <v>95</v>
+      </c>
+      <c r="I103" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" s="1">
+        <v>202703</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D104" s="1">
+        <v>3</v>
+      </c>
+      <c r="E104" s="1">
+        <v>76</v>
+      </c>
+      <c r="F104" s="1">
+        <v>95</v>
+      </c>
+      <c r="G104" s="1">
+        <v>87</v>
+      </c>
+      <c r="H104" s="1">
+        <v>40</v>
+      </c>
+      <c r="I104" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" s="1">
+        <v>202704</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D105" s="1">
+        <v>2</v>
+      </c>
+      <c r="E105" s="1">
         <v>56</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>202611</v>
-      </c>
-      <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12">
+      <c r="F105" s="1">
+        <v>57</v>
+      </c>
+      <c r="G105" s="1">
+        <v>67</v>
+      </c>
+      <c r="H105" s="1">
+        <v>94</v>
+      </c>
+      <c r="I105" s="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" s="1">
+        <v>202705</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D106" s="1">
+        <v>4</v>
+      </c>
+      <c r="E106" s="1">
+        <v>85</v>
+      </c>
+      <c r="F106" s="1">
+        <v>73</v>
+      </c>
+      <c r="G106" s="1">
+        <v>93</v>
+      </c>
+      <c r="H106" s="1">
+        <v>59</v>
+      </c>
+      <c r="I106" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107" s="1">
+        <v>202706</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D107" s="1">
+        <v>5</v>
+      </c>
+      <c r="E107" s="1">
+        <v>87</v>
+      </c>
+      <c r="F107" s="1">
+        <v>78</v>
+      </c>
+      <c r="G107" s="1">
+        <v>54</v>
+      </c>
+      <c r="H107" s="1">
+        <v>47</v>
+      </c>
+      <c r="I107" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" s="1">
+        <v>202707</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D108" s="1">
+        <v>5</v>
+      </c>
+      <c r="E108" s="1">
+        <v>100</v>
+      </c>
+      <c r="F108" s="1">
+        <v>78</v>
+      </c>
+      <c r="G108" s="1">
+        <v>83</v>
+      </c>
+      <c r="H108" s="1">
+        <v>56</v>
+      </c>
+      <c r="I108" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" s="1">
+        <v>202708</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D109" s="1">
+        <v>4</v>
+      </c>
+      <c r="E109" s="1">
+        <v>62</v>
+      </c>
+      <c r="F109" s="1">
+        <v>86</v>
+      </c>
+      <c r="G109" s="1">
+        <v>52</v>
+      </c>
+      <c r="H109" s="1">
+        <v>88</v>
+      </c>
+      <c r="I109" s="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" s="1">
+        <v>202709</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D110" s="1">
+        <v>1</v>
+      </c>
+      <c r="E110" s="1">
+        <v>57</v>
+      </c>
+      <c r="F110" s="1">
+        <v>95</v>
+      </c>
+      <c r="G110" s="1">
+        <v>97</v>
+      </c>
+      <c r="H110" s="1">
+        <v>64</v>
+      </c>
+      <c r="I110" s="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" s="1">
+        <v>202710</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D111" s="1">
+        <v>2</v>
+      </c>
+      <c r="E111" s="1">
+        <v>91</v>
+      </c>
+      <c r="F111" s="1">
+        <v>46</v>
+      </c>
+      <c r="G111" s="1">
+        <v>88</v>
+      </c>
+      <c r="H111" s="1">
+        <v>57</v>
+      </c>
+      <c r="I111" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" s="1">
+        <v>202711</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D112" s="1">
+        <v>1</v>
+      </c>
+      <c r="E112" s="1">
+        <v>99</v>
+      </c>
+      <c r="F112" s="1">
+        <v>81</v>
+      </c>
+      <c r="G112" s="1">
+        <v>87</v>
+      </c>
+      <c r="H112" s="1">
+        <v>72</v>
+      </c>
+      <c r="I112" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113" s="1">
+        <v>202712</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D113" s="1">
         <v>3</v>
       </c>
-      <c r="E12">
+      <c r="E113" s="1">
+        <v>54</v>
+      </c>
+      <c r="F113" s="1">
         <v>96</v>
       </c>
-      <c r="F12">
+      <c r="G113" s="1">
+        <v>48</v>
+      </c>
+      <c r="H113" s="1">
+        <v>67</v>
+      </c>
+      <c r="I113" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" s="1">
+        <v>202713</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114" s="1">
+        <v>1</v>
+      </c>
+      <c r="E114" s="1">
+        <v>76</v>
+      </c>
+      <c r="F114" s="1">
+        <v>70</v>
+      </c>
+      <c r="G114" s="1">
+        <v>92</v>
+      </c>
+      <c r="H114" s="1">
+        <v>93</v>
+      </c>
+      <c r="I114" s="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115" s="1">
+        <v>202714</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D115" s="1">
+        <v>4</v>
+      </c>
+      <c r="E115" s="1">
+        <v>96</v>
+      </c>
+      <c r="F115" s="1">
+        <v>77</v>
+      </c>
+      <c r="G115" s="1">
+        <v>41</v>
+      </c>
+      <c r="H115" s="1">
+        <v>66</v>
+      </c>
+      <c r="I115" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" s="1">
+        <v>202715</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D116" s="1">
+        <v>5</v>
+      </c>
+      <c r="E116" s="1">
+        <v>46</v>
+      </c>
+      <c r="F116" s="1">
+        <v>71</v>
+      </c>
+      <c r="G116" s="1">
+        <v>72</v>
+      </c>
+      <c r="H116" s="1">
+        <v>64</v>
+      </c>
+      <c r="I116" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117" s="1">
+        <v>202716</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D117" s="1">
+        <v>2</v>
+      </c>
+      <c r="E117" s="1">
+        <v>57</v>
+      </c>
+      <c r="F117" s="1">
+        <v>93</v>
+      </c>
+      <c r="G117" s="1">
+        <v>56</v>
+      </c>
+      <c r="H117" s="1">
+        <v>87</v>
+      </c>
+      <c r="I117" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="A118" s="1">
+        <v>202717</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D118" s="1">
+        <v>4</v>
+      </c>
+      <c r="E118" s="1">
+        <v>69</v>
+      </c>
+      <c r="F118" s="1">
+        <v>81</v>
+      </c>
+      <c r="G118" s="1">
+        <v>78</v>
+      </c>
+      <c r="H118" s="1">
+        <v>92</v>
+      </c>
+      <c r="I118" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
+      <c r="A119" s="1">
+        <v>202718</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D119" s="1">
+        <v>5</v>
+      </c>
+      <c r="E119" s="1">
+        <v>69</v>
+      </c>
+      <c r="F119" s="1">
+        <v>91</v>
+      </c>
+      <c r="G119" s="1">
+        <v>54</v>
+      </c>
+      <c r="H119" s="1">
+        <v>99</v>
+      </c>
+      <c r="I119" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="A120" s="1">
+        <v>202719</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D120" s="1">
+        <v>1</v>
+      </c>
+      <c r="E120" s="1">
+        <v>89</v>
+      </c>
+      <c r="F120" s="1">
+        <v>67</v>
+      </c>
+      <c r="G120" s="1">
+        <v>60</v>
+      </c>
+      <c r="H120" s="1">
+        <v>48</v>
+      </c>
+      <c r="I120" s="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="A121" s="1">
+        <v>202720</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D121" s="1">
+        <v>3</v>
+      </c>
+      <c r="E121" s="1">
+        <v>41</v>
+      </c>
+      <c r="F121" s="1">
+        <v>75</v>
+      </c>
+      <c r="G121" s="1">
+        <v>98</v>
+      </c>
+      <c r="H121" s="1">
+        <v>89</v>
+      </c>
+      <c r="I121" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
+      <c r="A122" s="1">
+        <v>202721</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D122" s="1">
+        <v>3</v>
+      </c>
+      <c r="E122" s="1">
+        <v>85</v>
+      </c>
+      <c r="F122" s="1">
+        <v>93</v>
+      </c>
+      <c r="G122" s="1">
+        <v>81</v>
+      </c>
+      <c r="H122" s="1">
+        <v>67</v>
+      </c>
+      <c r="I122" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
+      <c r="A123" s="1">
+        <v>202722</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D123" s="1">
+        <v>2</v>
+      </c>
+      <c r="E123" s="1">
+        <v>87</v>
+      </c>
+      <c r="F123" s="1">
+        <v>73</v>
+      </c>
+      <c r="G123" s="1">
+        <v>41</v>
+      </c>
+      <c r="H123" s="1">
+        <v>52</v>
+      </c>
+      <c r="I123" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
+      <c r="A124" s="1">
+        <v>202723</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D124" s="1">
+        <v>5</v>
+      </c>
+      <c r="E124" s="1">
+        <v>75</v>
+      </c>
+      <c r="F124" s="1">
+        <v>68</v>
+      </c>
+      <c r="G124" s="1">
+        <v>73</v>
+      </c>
+      <c r="H124" s="1">
+        <v>100</v>
+      </c>
+      <c r="I124" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
+      <c r="A125" s="1">
+        <v>202724</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D125" s="1">
+        <v>4</v>
+      </c>
+      <c r="E125" s="1">
+        <v>68</v>
+      </c>
+      <c r="F125" s="1">
+        <v>52</v>
+      </c>
+      <c r="G125" s="1">
         <v>94</v>
       </c>
-      <c r="G12">
+      <c r="H125" s="1">
+        <v>74</v>
+      </c>
+      <c r="I125" s="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126" s="1">
+        <v>202725</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D126" s="1">
+        <v>4</v>
+      </c>
+      <c r="E126" s="1">
+        <v>50</v>
+      </c>
+      <c r="F126" s="1">
+        <v>84</v>
+      </c>
+      <c r="G126" s="1">
+        <v>86</v>
+      </c>
+      <c r="H126" s="1">
+        <v>75</v>
+      </c>
+      <c r="I126" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="A127" s="1">
+        <v>202726</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D127" s="1">
+        <v>4</v>
+      </c>
+      <c r="E127" s="1">
+        <v>81</v>
+      </c>
+      <c r="F127" s="1">
+        <v>80</v>
+      </c>
+      <c r="G127" s="1">
+        <v>72</v>
+      </c>
+      <c r="H127" s="1">
+        <v>85</v>
+      </c>
+      <c r="I127" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128" s="1">
+        <v>202727</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D128" s="1">
+        <v>3</v>
+      </c>
+      <c r="E128" s="1">
+        <v>53</v>
+      </c>
+      <c r="F128" s="1">
+        <v>52</v>
+      </c>
+      <c r="G128" s="1">
+        <v>89</v>
+      </c>
+      <c r="H128" s="1">
+        <v>81</v>
+      </c>
+      <c r="I128" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" s="1">
+        <v>202728</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D129" s="1">
+        <v>4</v>
+      </c>
+      <c r="E129" s="1">
+        <v>94</v>
+      </c>
+      <c r="F129" s="1">
+        <v>90</v>
+      </c>
+      <c r="G129" s="1">
+        <v>83</v>
+      </c>
+      <c r="H129" s="1">
+        <v>44</v>
+      </c>
+      <c r="I129" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130" s="1">
+        <v>202729</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D130" s="1">
+        <v>2</v>
+      </c>
+      <c r="E130" s="1">
+        <v>90</v>
+      </c>
+      <c r="F130" s="1">
+        <v>79</v>
+      </c>
+      <c r="G130" s="1">
+        <v>69</v>
+      </c>
+      <c r="H130" s="1">
+        <v>83</v>
+      </c>
+      <c r="I130" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131" s="1">
+        <v>202730</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D131" s="1">
+        <v>4</v>
+      </c>
+      <c r="E131" s="1">
+        <v>54</v>
+      </c>
+      <c r="F131" s="1">
+        <v>47</v>
+      </c>
+      <c r="G131" s="1">
+        <v>73</v>
+      </c>
+      <c r="H131" s="1">
+        <v>89</v>
+      </c>
+      <c r="I131" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" s="1">
+        <v>202731</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D132" s="1">
+        <v>3</v>
+      </c>
+      <c r="E132" s="1">
+        <v>92</v>
+      </c>
+      <c r="F132" s="1">
+        <v>57</v>
+      </c>
+      <c r="G132" s="1">
+        <v>99</v>
+      </c>
+      <c r="H132" s="1">
+        <v>55</v>
+      </c>
+      <c r="I132" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" s="1">
+        <v>202732</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D133" s="1">
+        <v>2</v>
+      </c>
+      <c r="E133" s="1">
+        <v>97</v>
+      </c>
+      <c r="F133" s="1">
+        <v>86</v>
+      </c>
+      <c r="G133" s="1">
+        <v>51</v>
+      </c>
+      <c r="H133" s="1">
+        <v>64</v>
+      </c>
+      <c r="I133" s="1">
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>202612</v>
-      </c>
-      <c r="B13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13">
+    <row r="134" spans="1:9">
+      <c r="A134" s="1">
+        <v>202733</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D134" s="1">
+        <v>5</v>
+      </c>
+      <c r="E134" s="1">
+        <v>65</v>
+      </c>
+      <c r="F134" s="1">
+        <v>79</v>
+      </c>
+      <c r="G134" s="1">
+        <v>86</v>
+      </c>
+      <c r="H134" s="1">
+        <v>99</v>
+      </c>
+      <c r="I134" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="A135" s="1">
+        <v>202734</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D135" s="1">
+        <v>3</v>
+      </c>
+      <c r="E135" s="1">
+        <v>90</v>
+      </c>
+      <c r="F135" s="1">
+        <v>40</v>
+      </c>
+      <c r="G135" s="1">
+        <v>98</v>
+      </c>
+      <c r="H135" s="1">
+        <v>65</v>
+      </c>
+      <c r="I135" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
+      <c r="A136" s="1">
+        <v>202735</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D136" s="1">
+        <v>3</v>
+      </c>
+      <c r="E136" s="1">
+        <v>50</v>
+      </c>
+      <c r="F136" s="1">
+        <v>61</v>
+      </c>
+      <c r="G136" s="1">
+        <v>71</v>
+      </c>
+      <c r="H136" s="1">
+        <v>95</v>
+      </c>
+      <c r="I136" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
+      <c r="A137" s="1">
+        <v>202736</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D137" s="1">
+        <v>1</v>
+      </c>
+      <c r="E137" s="1">
+        <v>93</v>
+      </c>
+      <c r="F137" s="1">
+        <v>72</v>
+      </c>
+      <c r="G137" s="1">
+        <v>67</v>
+      </c>
+      <c r="H137" s="1">
+        <v>81</v>
+      </c>
+      <c r="I137" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138" s="1">
+        <v>202737</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D138" s="1">
+        <v>3</v>
+      </c>
+      <c r="E138" s="1">
+        <v>44</v>
+      </c>
+      <c r="F138" s="1">
+        <v>64</v>
+      </c>
+      <c r="G138" s="1">
+        <v>73</v>
+      </c>
+      <c r="H138" s="1">
+        <v>74</v>
+      </c>
+      <c r="I138" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
+      <c r="A139" s="1">
+        <v>202738</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D139" s="1">
+        <v>3</v>
+      </c>
+      <c r="E139" s="1">
+        <v>55</v>
+      </c>
+      <c r="F139" s="1">
+        <v>42</v>
+      </c>
+      <c r="G139" s="1">
+        <v>50</v>
+      </c>
+      <c r="H139" s="1">
+        <v>64</v>
+      </c>
+      <c r="I139" s="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
+      <c r="A140" s="1">
+        <v>202739</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D140" s="1">
+        <v>5</v>
+      </c>
+      <c r="E140" s="1">
+        <v>87</v>
+      </c>
+      <c r="F140" s="1">
+        <v>59</v>
+      </c>
+      <c r="G140" s="1">
+        <v>66</v>
+      </c>
+      <c r="H140" s="1">
+        <v>63</v>
+      </c>
+      <c r="I140" s="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
+      <c r="A141" s="1">
+        <v>202740</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D141" s="1">
         <v>4</v>
       </c>
-      <c r="E13">
+      <c r="E141" s="1">
+        <v>97</v>
+      </c>
+      <c r="F141" s="1">
+        <v>74</v>
+      </c>
+      <c r="G141" s="1">
+        <v>66</v>
+      </c>
+      <c r="H141" s="1">
+        <v>87</v>
+      </c>
+      <c r="I141" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
+      <c r="A142" s="1">
+        <v>202741</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D142" s="1">
+        <v>5</v>
+      </c>
+      <c r="E142" s="1">
+        <v>54</v>
+      </c>
+      <c r="F142" s="1">
+        <v>88</v>
+      </c>
+      <c r="G142" s="1">
+        <v>100</v>
+      </c>
+      <c r="H142" s="1">
+        <v>55</v>
+      </c>
+      <c r="I142" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
+      <c r="A143" s="1">
+        <v>202742</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D143" s="1">
+        <v>1</v>
+      </c>
+      <c r="E143" s="1">
+        <v>77</v>
+      </c>
+      <c r="F143" s="1">
+        <v>91</v>
+      </c>
+      <c r="G143" s="1">
+        <v>46</v>
+      </c>
+      <c r="H143" s="1">
+        <v>72</v>
+      </c>
+      <c r="I143" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
+      <c r="A144" s="1">
+        <v>202743</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D144" s="1">
+        <v>1</v>
+      </c>
+      <c r="E144" s="1">
+        <v>50</v>
+      </c>
+      <c r="F144" s="1">
+        <v>83</v>
+      </c>
+      <c r="G144" s="1">
+        <v>55</v>
+      </c>
+      <c r="H144" s="1">
         <v>61</v>
       </c>
-      <c r="F13">
+      <c r="I144" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
+      <c r="A145" s="1">
+        <v>202744</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D145" s="1">
+        <v>1</v>
+      </c>
+      <c r="E145" s="1">
+        <v>78</v>
+      </c>
+      <c r="F145" s="1">
+        <v>43</v>
+      </c>
+      <c r="G145" s="1">
+        <v>76</v>
+      </c>
+      <c r="H145" s="1">
+        <v>53</v>
+      </c>
+      <c r="I145" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
+      <c r="A146" s="1">
+        <v>202745</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D146" s="1">
+        <v>2</v>
+      </c>
+      <c r="E146" s="1">
+        <v>92</v>
+      </c>
+      <c r="F146" s="1">
+        <v>97</v>
+      </c>
+      <c r="G146" s="1">
+        <v>63</v>
+      </c>
+      <c r="H146" s="1">
+        <v>97</v>
+      </c>
+      <c r="I146" s="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
+      <c r="A147" s="1">
+        <v>202746</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D147" s="1">
+        <v>1</v>
+      </c>
+      <c r="E147" s="1">
+        <v>93</v>
+      </c>
+      <c r="F147" s="1">
+        <v>65</v>
+      </c>
+      <c r="G147" s="1">
+        <v>96</v>
+      </c>
+      <c r="H147" s="1">
+        <v>92</v>
+      </c>
+      <c r="I147" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="A148" s="1">
+        <v>202747</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D148" s="1">
+        <v>4</v>
+      </c>
+      <c r="E148" s="1">
+        <v>82</v>
+      </c>
+      <c r="F148" s="1">
+        <v>80</v>
+      </c>
+      <c r="G148" s="1">
+        <v>47</v>
+      </c>
+      <c r="H148" s="1">
+        <v>67</v>
+      </c>
+      <c r="I148" s="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="A149" s="1">
+        <v>202748</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D149" s="1">
+        <v>1</v>
+      </c>
+      <c r="E149" s="1">
+        <v>83</v>
+      </c>
+      <c r="F149" s="1">
+        <v>72</v>
+      </c>
+      <c r="G149" s="1">
+        <v>58</v>
+      </c>
+      <c r="H149" s="1">
+        <v>51</v>
+      </c>
+      <c r="I149" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150" s="1">
+        <v>202749</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D150" s="1">
+        <v>4</v>
+      </c>
+      <c r="E150" s="1">
+        <v>72</v>
+      </c>
+      <c r="F150" s="1">
+        <v>85</v>
+      </c>
+      <c r="G150" s="1">
+        <v>40</v>
+      </c>
+      <c r="H150" s="1">
+        <v>78</v>
+      </c>
+      <c r="I150" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" s="1">
+        <v>202750</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D151" s="1">
+        <v>4</v>
+      </c>
+      <c r="E151" s="1">
+        <v>61</v>
+      </c>
+      <c r="F151" s="1">
+        <v>43</v>
+      </c>
+      <c r="G151" s="1">
+        <v>51</v>
+      </c>
+      <c r="H151" s="1">
+        <v>80</v>
+      </c>
+      <c r="I151" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
+      <c r="A152" s="1">
+        <v>202751</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D152" s="1">
+        <v>1</v>
+      </c>
+      <c r="E152" s="1">
+        <v>94</v>
+      </c>
+      <c r="F152" s="1">
+        <v>70</v>
+      </c>
+      <c r="G152" s="1">
+        <v>40</v>
+      </c>
+      <c r="H152" s="1">
+        <v>94</v>
+      </c>
+      <c r="I152" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
+      <c r="A153" s="1">
+        <v>202752</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D153" s="1">
+        <v>1</v>
+      </c>
+      <c r="E153" s="1">
+        <v>86</v>
+      </c>
+      <c r="F153" s="1">
+        <v>97</v>
+      </c>
+      <c r="G153" s="1">
+        <v>68</v>
+      </c>
+      <c r="H153" s="1">
+        <v>83</v>
+      </c>
+      <c r="I153" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
+      <c r="A154" s="1">
+        <v>202753</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D154" s="1">
+        <v>1</v>
+      </c>
+      <c r="E154" s="1">
+        <v>68</v>
+      </c>
+      <c r="F154" s="1">
         <v>64</v>
       </c>
-      <c r="G13">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>202613</v>
-      </c>
-      <c r="B14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14">
-        <v>63</v>
-      </c>
-      <c r="F14">
-        <v>82</v>
-      </c>
-      <c r="G14">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>202614</v>
-      </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15">
-        <v>3</v>
-      </c>
-      <c r="E15">
-        <v>61</v>
-      </c>
-      <c r="F15">
-        <v>51</v>
-      </c>
-      <c r="G15">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>202615</v>
-      </c>
-      <c r="B16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>58</v>
-      </c>
-      <c r="F16">
-        <v>79</v>
-      </c>
-      <c r="G16">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>202616</v>
-      </c>
-      <c r="B17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17">
-        <v>2</v>
-      </c>
-      <c r="E17">
-        <v>56</v>
-      </c>
-      <c r="F17">
+      <c r="G154" s="1">
+        <v>54</v>
+      </c>
+      <c r="H154" s="1">
+        <v>40</v>
+      </c>
+      <c r="I154" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
+      <c r="A155" s="1">
+        <v>202754</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D155" s="1">
+        <v>5</v>
+      </c>
+      <c r="E155" s="1">
+        <v>57</v>
+      </c>
+      <c r="F155" s="1">
+        <v>64</v>
+      </c>
+      <c r="G155" s="1">
         <v>45</v>
       </c>
-      <c r="G17">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>202617</v>
-      </c>
-      <c r="B18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18">
-        <v>80</v>
-      </c>
-      <c r="F18">
-        <v>93</v>
-      </c>
-      <c r="G18">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>202618</v>
-      </c>
-      <c r="B19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19">
-        <v>5</v>
-      </c>
-      <c r="E19">
-        <v>56</v>
-      </c>
-      <c r="F19">
-        <v>91</v>
-      </c>
-      <c r="G19">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>202619</v>
-      </c>
-      <c r="B20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20">
-        <v>3</v>
-      </c>
-      <c r="E20">
-        <v>42</v>
-      </c>
-      <c r="F20">
-        <v>65</v>
-      </c>
-      <c r="G20">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>202620</v>
-      </c>
-      <c r="B21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-      <c r="E21">
-        <v>83</v>
-      </c>
-      <c r="F21">
-        <v>99</v>
-      </c>
-      <c r="G21">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>202621</v>
-      </c>
-      <c r="B22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22">
-        <v>4</v>
-      </c>
-      <c r="E22">
-        <v>72</v>
-      </c>
-      <c r="F22">
-        <v>81</v>
-      </c>
-      <c r="G22">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>202622</v>
-      </c>
-      <c r="B23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23">
-        <v>4</v>
-      </c>
-      <c r="E23">
-        <v>89</v>
-      </c>
-      <c r="F23">
-        <v>93</v>
-      </c>
-      <c r="G23">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>202623</v>
-      </c>
-      <c r="B24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24">
-        <v>5</v>
-      </c>
-      <c r="E24">
-        <v>73</v>
-      </c>
-      <c r="F24">
-        <v>65</v>
-      </c>
-      <c r="G24">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>202624</v>
-      </c>
-      <c r="B25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25">
-        <v>4</v>
-      </c>
-      <c r="E25">
-        <v>53</v>
-      </c>
-      <c r="F25">
-        <v>72</v>
-      </c>
-      <c r="G25">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>202625</v>
-      </c>
-      <c r="B26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26">
-        <v>4</v>
-      </c>
-      <c r="E26">
-        <v>95</v>
-      </c>
-      <c r="F26">
-        <v>25</v>
-      </c>
-      <c r="G26">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>202626</v>
-      </c>
-      <c r="B27" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27">
-        <v>2</v>
-      </c>
-      <c r="E27">
-        <v>62</v>
-      </c>
-      <c r="F27">
-        <v>82</v>
-      </c>
-      <c r="G27">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>202627</v>
-      </c>
-      <c r="B28" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28">
-        <v>3</v>
-      </c>
-      <c r="E28">
-        <v>70</v>
-      </c>
-      <c r="F28">
-        <v>63</v>
-      </c>
-      <c r="G28">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>202628</v>
-      </c>
-      <c r="B29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29">
-        <v>3</v>
-      </c>
-      <c r="E29">
-        <v>77</v>
-      </c>
-      <c r="F29">
-        <v>49</v>
-      </c>
-      <c r="G29">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>202629</v>
-      </c>
-      <c r="B30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30">
-        <v>3</v>
-      </c>
-      <c r="E30">
-        <v>52</v>
-      </c>
-      <c r="F30">
-        <v>70</v>
-      </c>
-      <c r="G30">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>202630</v>
-      </c>
-      <c r="B31" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31">
-        <v>3</v>
-      </c>
-      <c r="E31">
-        <v>52</v>
-      </c>
-      <c r="F31">
-        <v>61</v>
-      </c>
-      <c r="G31">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>202631</v>
-      </c>
-      <c r="B32" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32">
-        <v>2</v>
-      </c>
-      <c r="E32">
-        <v>93</v>
-      </c>
-      <c r="F32">
-        <v>51</v>
-      </c>
-      <c r="G32">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>202632</v>
-      </c>
-      <c r="B33" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33">
-        <v>5</v>
-      </c>
-      <c r="E33">
-        <v>70</v>
-      </c>
-      <c r="F33">
-        <v>74</v>
-      </c>
-      <c r="G33">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>202633</v>
-      </c>
-      <c r="B34" t="s">
-        <v>41</v>
-      </c>
-      <c r="C34" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34">
-        <v>2</v>
-      </c>
-      <c r="E34">
-        <v>57</v>
-      </c>
-      <c r="F34">
-        <v>97</v>
-      </c>
-      <c r="G34">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>202634</v>
-      </c>
-      <c r="B35" t="s">
-        <v>42</v>
-      </c>
-      <c r="C35" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35">
-        <v>2</v>
-      </c>
-      <c r="E35">
-        <v>50</v>
-      </c>
-      <c r="F35">
-        <v>52</v>
-      </c>
-      <c r="G35">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>202635</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="H155" s="1">
+        <v>47</v>
+      </c>
+      <c r="I155" s="1">
         <v>43</v>
-      </c>
-      <c r="C36" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36">
-        <v>3</v>
-      </c>
-      <c r="E36">
-        <v>60</v>
-      </c>
-      <c r="F36">
-        <v>94</v>
-      </c>
-      <c r="G36">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>202636</v>
-      </c>
-      <c r="B37" t="s">
-        <v>44</v>
-      </c>
-      <c r="C37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37">
-        <v>4</v>
-      </c>
-      <c r="E37">
-        <v>89</v>
-      </c>
-      <c r="F37">
-        <v>59</v>
-      </c>
-      <c r="G37">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>202637</v>
-      </c>
-      <c r="B38" t="s">
-        <v>45</v>
-      </c>
-      <c r="C38" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-      <c r="E38">
-        <v>96</v>
-      </c>
-      <c r="F38">
-        <v>53</v>
-      </c>
-      <c r="G38">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>202638</v>
-      </c>
-      <c r="B39" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39">
-        <v>2</v>
-      </c>
-      <c r="E39">
-        <v>49</v>
-      </c>
-      <c r="F39">
-        <v>20</v>
-      </c>
-      <c r="G39">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>202639</v>
-      </c>
-      <c r="B40" t="s">
-        <v>47</v>
-      </c>
-      <c r="C40" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40">
-        <v>2</v>
-      </c>
-      <c r="E40">
-        <v>73</v>
-      </c>
-      <c r="F40">
-        <v>93</v>
-      </c>
-      <c r="G40">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>202640</v>
-      </c>
-      <c r="B41" t="s">
-        <v>48</v>
-      </c>
-      <c r="C41" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41">
-        <v>2</v>
-      </c>
-      <c r="E41">
-        <v>56</v>
-      </c>
-      <c r="F41">
-        <v>95</v>
-      </c>
-      <c r="G41">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>202641</v>
-      </c>
-      <c r="B42" t="s">
-        <v>49</v>
-      </c>
-      <c r="C42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-      <c r="E42">
-        <v>92</v>
-      </c>
-      <c r="F42">
-        <v>95</v>
-      </c>
-      <c r="G42">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>202642</v>
-      </c>
-      <c r="B43" t="s">
-        <v>50</v>
-      </c>
-      <c r="C43" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-      <c r="E43">
-        <v>53</v>
-      </c>
-      <c r="F43">
-        <v>72</v>
-      </c>
-      <c r="G43">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>202643</v>
-      </c>
-      <c r="B44" t="s">
-        <v>51</v>
-      </c>
-      <c r="C44" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="E44">
-        <v>58</v>
-      </c>
-      <c r="F44">
-        <v>86</v>
-      </c>
-      <c r="G44">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>202644</v>
-      </c>
-      <c r="B45" t="s">
-        <v>52</v>
-      </c>
-      <c r="C45" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45">
-        <v>5</v>
-      </c>
-      <c r="E45">
-        <v>56</v>
-      </c>
-      <c r="F45">
-        <v>70</v>
-      </c>
-      <c r="G45">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>202645</v>
-      </c>
-      <c r="B46" t="s">
-        <v>53</v>
-      </c>
-      <c r="C46" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46">
-        <v>5</v>
-      </c>
-      <c r="E46">
-        <v>95</v>
-      </c>
-      <c r="F46">
-        <v>78</v>
-      </c>
-      <c r="G46">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>202646</v>
-      </c>
-      <c r="B47" t="s">
-        <v>54</v>
-      </c>
-      <c r="C47" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47">
-        <v>3</v>
-      </c>
-      <c r="E47">
-        <v>94</v>
-      </c>
-      <c r="F47">
-        <v>95</v>
-      </c>
-      <c r="G47">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>202647</v>
-      </c>
-      <c r="B48" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48">
-        <v>3</v>
-      </c>
-      <c r="E48">
-        <v>46</v>
-      </c>
-      <c r="F48">
-        <v>47</v>
-      </c>
-      <c r="G48">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>202648</v>
-      </c>
-      <c r="B49" t="s">
-        <v>56</v>
-      </c>
-      <c r="C49" t="s">
-        <v>10</v>
-      </c>
-      <c r="D49">
-        <v>3</v>
-      </c>
-      <c r="E49">
-        <v>77</v>
-      </c>
-      <c r="F49">
-        <v>56</v>
-      </c>
-      <c r="G49">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>202649</v>
-      </c>
-      <c r="B50" t="s">
-        <v>57</v>
-      </c>
-      <c r="C50" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="E50">
-        <v>93</v>
-      </c>
-      <c r="F50">
-        <v>56</v>
-      </c>
-      <c r="G50">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>202650</v>
-      </c>
-      <c r="B51" t="s">
-        <v>58</v>
-      </c>
-      <c r="C51" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51">
-        <v>4</v>
-      </c>
-      <c r="E51">
-        <v>89</v>
-      </c>
-      <c r="F51">
-        <v>50</v>
-      </c>
-      <c r="G51">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52">
-        <v>202651</v>
-      </c>
-      <c r="B52" t="s">
-        <v>59</v>
-      </c>
-      <c r="C52" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52">
-        <v>2</v>
-      </c>
-      <c r="E52">
-        <v>75</v>
-      </c>
-      <c r="F52">
-        <v>72</v>
-      </c>
-      <c r="G52">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53">
-        <v>202652</v>
-      </c>
-      <c r="B53" t="s">
-        <v>60</v>
-      </c>
-      <c r="C53" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53">
-        <v>3</v>
-      </c>
-      <c r="E53">
-        <v>60</v>
-      </c>
-      <c r="F53">
-        <v>89</v>
-      </c>
-      <c r="G53">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54">
-        <v>202653</v>
-      </c>
-      <c r="B54" t="s">
-        <v>61</v>
-      </c>
-      <c r="C54" t="s">
-        <v>10</v>
-      </c>
-      <c r="D54">
-        <v>4</v>
-      </c>
-      <c r="E54">
-        <v>76</v>
-      </c>
-      <c r="F54">
-        <v>100</v>
-      </c>
-      <c r="G54">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55">
-        <v>202654</v>
-      </c>
-      <c r="B55" t="s">
-        <v>62</v>
-      </c>
-      <c r="C55" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55">
-        <v>4</v>
-      </c>
-      <c r="E55">
-        <v>81</v>
-      </c>
-      <c r="F55">
-        <v>53</v>
-      </c>
-      <c r="G55">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56">
-        <v>202655</v>
-      </c>
-      <c r="B56" t="s">
-        <v>63</v>
-      </c>
-      <c r="C56" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56">
-        <v>1</v>
-      </c>
-      <c r="E56">
-        <v>41</v>
-      </c>
-      <c r="F56">
-        <v>98</v>
-      </c>
-      <c r="G56">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
